--- a/4.evidence/ITGC/SAP_SUIM_ActiveUserList_2025Q4.xlsx
+++ b/4.evidence/ITGC/SAP_SUIM_ActiveUserList_2025Q4.xlsx
@@ -531,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SAP SUIM / Active User List Export - 2025Q4</t>
+          <t>SAP SUIM / Active User List Export - 2025Q4 [※ヘッダ情報一部欠落]</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       <c r="B2" s="3" t="n"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-03-31 14:45:45</t>
+          <t>(判別不能 - 再出力依頼中)</t>
         </is>
       </c>
       <c r="D2" s="4" t="n"/>
@@ -598,7 +598,7 @@
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Status = Active / Client = 100 (Production)</t>
+          <t>(条件指定の証跡なし - 再出力依頼中)</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
@@ -1783,8 +1783,8 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:B4"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A2:B2"/>
